--- a/erp_exchange/samples/valid_erp_export.xlsx
+++ b/erp_exchange/samples/valid_erp_export.xlsx
@@ -408,7 +408,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BOOK1002</t>
+          <t>9780547928227</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -426,7 +426,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BOOK1001</t>
+          <t>9780451524935</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
